--- a/Output/FullPartlist.xlsx
+++ b/Output/FullPartlist.xlsx
@@ -79,7 +79,7 @@
     <x:t>ParentName</x:t>
   </x:si>
   <x:si>
-    <x:t>LCAMP Mobile Robot</x:t>
+    <x:t>LCamp Robot</x:t>
   </x:si>
   <x:si>
     <x:t>Component</x:t>
@@ -94,34 +94,31 @@
     <x:t>LCAMPRobot</x:t>
   </x:si>
   <x:si>
+    <x:t>DC-Drive</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Drive</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Drive System of the Robot</x:t>
+  </x:si>
+  <x:si>
     <x:t>Drive bl</x:t>
   </x:si>
   <x:si>
-    <x:t>Frame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lopkalisierung für  Drive back left</x:t>
-  </x:si>
-  <x:si>
     <x:t>PartDescription</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [-100.00, 70.00, 0.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [L:100, W:50, H:61]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DC-Drive</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Drive</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The Drive System of the Robot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Device</x:t>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 32.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [L:50, W:45, H:64]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Material</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Color [A=255, R=255, G=255, B=255]</x:t>
   </x:si>
   <x:si>
     <x:t>HolderBase</x:t>
@@ -142,9 +139,6 @@
     <x:t>Fixed, null</x:t>
   </x:si>
   <x:si>
-    <x:t>Material</x:t>
-  </x:si>
-  <x:si>
     <x:t>DC_Holder_64.stl</x:t>
   </x:si>
   <x:si>
@@ -172,7 +166,7 @@
     <x:t>MotorController.stl</x:t>
   </x:si>
   <x:si>
-    <x:t>Regular-Wheel</x:t>
+    <x:t>Omni-Wheel</x:t>
   </x:si>
   <x:si>
     <x:t>Wheel</x:t>
@@ -181,6 +175,12 @@
     <x:t>The Wheel of the Robot</x:t>
   </x:si>
   <x:si>
+    <x:t>JointType: Continuous,  (XYZ) [0.00, 5.00, 0.00][mm], (RPY) [-90.00, 0.00, 0.00][grad], (BOX) [None]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Color [A=255, R=192, G=192, B=192]</x:t>
+  </x:si>
+  <x:si>
     <x:t>Wheel-Hub</x:t>
   </x:si>
   <x:si>
@@ -190,37 +190,49 @@
     <x:t>Hub for Regular-Wheel as 3D Printed Part</x:t>
   </x:si>
   <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 1.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:40, R:20]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>wheel_hub_ax.stl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rim-inner</x:t>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 1.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [None]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wheel_Hub_ax.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rim_inner_a</x:t>
   </x:si>
   <x:si>
     <x:t>Rimm</x:t>
   </x:si>
   <x:si>
-    <x:t>Inner Rim for Regular-Wheel as 3D Printed Part</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 2.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:40, R:20]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Regular_Wheel_Star_30_84.stl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rim-outer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Outer Rim for Regular-Wheel as 3D Printed Part</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 28.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:40, R:20]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Regular_Wheel_Star_24_84.stl</x:t>
+    <x:t>Rim for Omni-Wheel as 3D Printed Parf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 2.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [None]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OmniWheel_Star_2a.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rim_inner_b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 5.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [None]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OmniWheel_Star_2b.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rim_outer_a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 26.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [None]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OmniWheel_Star_1.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rim_outer_b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 32.00][mm], (RPY) [0.00, 180.00, 0.00][grad], (BOX) [None]</x:t>
   </x:si>
   <x:si>
     <x:t>Wheel-Hub-Cap</x:t>
@@ -229,117 +241,168 @@
     <x:t>HubCap</x:t>
   </x:si>
   <x:si>
-    <x:t>Hub Cup for Regular-Wheel as 3D Printed Part</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 28.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:20, R:40]</x:t>
+    <x:t>Hub Cup for Omni-Wheel as 3D Printed Part</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 34.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:8, R:20]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Color [A=255, R=100, G=149, B=237]</x:t>
   </x:si>
   <x:si>
     <x:t>Hub_Cup_8.stl</x:t>
   </x:si>
   <x:si>
+    <x:t>Rollers_a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assembly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>inner Rollers for Omni-wheel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6,  RotZ, alfa=90°, r=38mm, phi=30°</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Continuous,  (XYZ) [0.00, 0.00, 8.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [None]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OmniWheel_Roller_2.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Roller</x:t>
+  </x:si>
+  <x:si>
     <x:t>Tire</x:t>
   </x:si>
   <x:si>
-    <x:t>Tire for Regular-Wheel as 3D Printed Part</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 15.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:30, R:48]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wheel_92_outside.stl</x:t>
+    <x:t>Rollers_a [6,  RotZ, alfa=90°, r=38mm, phi=30°]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Continuous,  (XYZ) [0.00, 0.00, 31.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [None]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Color [A=255, R=0, G=0, B=0]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RollerPin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Norm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Roller Pins for Omni Wheel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Color [A=255, R=128, G=128, B=128]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>grey</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pin_Roller.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rollers_b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>outer Rollers for Omni-wheel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6,  RotZ, alfa=90°, r=38mm, phi=0°</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Continuous,  (XYZ) [0.00, 0.00, 28.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [None]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rollers_b [6,  RotZ, alfa=90°, r=38mm, phi=0°]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Continuous,  (XYZ) [0.00, 0.00, 6.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [None]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pin for Roller in Omni-Wheel</x:t>
   </x:si>
   <x:si>
     <x:t>Drive br</x:t>
   </x:si>
   <x:si>
-    <x:t>Lopkalisierung für Drive back right</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [-100.00, -70.00, 0.00][mm], (RPY) [0.00, 0.00, 180.00][grad], (BOX) [L:100, W:50, H:61]</x:t>
-  </x:si>
-  <x:si>
     <x:t>Drive fl</x:t>
   </x:si>
   <x:si>
-    <x:t>Lopkalisierung für Drive front left</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [100.00, 70.00, 0.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [L:100, W:50, H:61]</x:t>
-  </x:si>
-  <x:si>
     <x:t>Drive fr</x:t>
   </x:si>
   <x:si>
-    <x:t>Lopkalisierung für Drive front right</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [100.00, -70.00, 0.00][mm], (RPY) [0.00, 0.00, 180.00][grad], (BOX) [L:100, W:50, H:61]</x:t>
+    <x:t>Sensorbox curved</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SensorBox</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Sensorbox on Front of the Robot</x:t>
   </x:si>
   <x:si>
     <x:t>Sensorbox front</x:t>
   </x:si>
   <x:si>
-    <x:t>Lopkalisierung für Sensorbox front</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [150.00, 0.00, 0.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [L:40, W:210, H:64]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sensorbox curved</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SensorBox</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The Sensorbox on Front of the Robot</x:t>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, -32.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [L:40, W:210, H:64]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Color [A=255, R=0, G=0, B=255]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lidar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sensor</x:t>
   </x:si>
   <x:si>
     <x:t>Sensor 1</x:t>
   </x:si>
   <x:si>
-    <x:t>Lopkalisierung für Sensor 1 ganz links</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [15.00, 65.00, 32.00][mm], (RPY) [15.00, 90.00, 0.00][grad], (BOX) [H:30, R:20]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LED-Light</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sensor</x:t>
+    <x:t>Base</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sensor Base Part as 3D Printed Parf for Lidar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SensorBase_li.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sensor PCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sensor pcb for Lidar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 10.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:10, R:20]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LidarSensorpcb.stl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Top</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sensor Cover for Lidar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 20.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [H:10, R:20]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SensorTop_li.stl</x:t>
   </x:si>
   <x:si>
     <x:t>Sensor 2</x:t>
   </x:si>
   <x:si>
-    <x:t>Lopkalisierung für Sensor 2 mitte links</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [25.00, 23.00, 32.00][mm], (RPY) [0.00, 90.00, 0.00][grad], (BOX) [H:30, R:20]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lidar</x:t>
-  </x:si>
-  <x:si>
     <x:t>Sensor 3</x:t>
   </x:si>
   <x:si>
-    <x:t>Lopkalisierung für Sensor 3 mitte rechts</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [25.00, -23.00, 32.00][mm], (RPY) [0.00, 90.00, 0.00][grad], (BOX) [H:30, R:20]</x:t>
-  </x:si>
-  <x:si>
     <x:t>Sensor 4</x:t>
   </x:si>
   <x:si>
-    <x:t>Lopkalisierung für Sensor 4 ganz rechts</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [15.00, -65.00, 32.00][mm], (RPY) [-15.00, 90.00, 0.00][grad], (BOX) [H:30, R:20]</x:t>
-  </x:si>
-  <x:si>
     <x:t>sbFront</x:t>
   </x:si>
   <x:si>
@@ -364,34 +427,13 @@
     <x:t>Sensorbox back</x:t>
   </x:si>
   <x:si>
-    <x:t>Lopkalisierung für Sensorbox back</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [-150.00, 0.00, 0.00][mm], (RPY) [0.00, 0.00, 180.00][grad], (BOX) [L:40, W:210, H:64]</x:t>
-  </x:si>
-  <x:si>
     <x:t>Sensorbox center</x:t>
   </x:si>
   <x:si>
-    <x:t>Lopkalisierung für Sensorbox center</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [0.00, -70.00, 0.00][mm], (RPY) [0.00, 0.00, 180.00][grad], (BOX) [L:40, W:210, H:64]</x:t>
-  </x:si>
-  <x:si>
     <x:t>Te Sensorbox on Front of the Robot</x:t>
   </x:si>
   <x:si>
-    <x:t>Lopkalisierung für Sensor 1 vorn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [23.00, 30.00, -30.00][mm], (RPY) [-90.00, 0.00, 0.00][grad], (BOX) [H:40, R:20]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lopkalisierung für Sensor 2 hinten</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [-23.00, 30.00, -30.00][mm], (RPY) [-90.00, 0.00, 0.00][grad], (BOX) [H:40, R:20]</x:t>
+    <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, 32.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [L:100, W:40, H:61]</x:t>
   </x:si>
   <x:si>
     <x:t>sbCenter</x:t>
@@ -400,24 +442,12 @@
     <x:t>Sensorbox_small_64.stl</x:t>
   </x:si>
   <x:si>
-    <x:t>Norm</x:t>
+    <x:t>Controller</x:t>
   </x:si>
   <x:si>
     <x:t>Sensorbox controller</x:t>
   </x:si>
   <x:si>
-    <x:t>Lopkalisierung für Sensorbox Controller on the right</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JointType: Fixed,  (XYZ) [0.00, 70.00, 0.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [L:40, W:210, H:64]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Controller</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lopkalisierung für Sensor 2 hintens</x:t>
-  </x:si>
-  <x:si>
     <x:t>sb_center_cont</x:t>
   </x:si>
   <x:si>
@@ -445,7 +475,7 @@
     <x:t>Basplate Pexi</x:t>
   </x:si>
   <x:si>
-    <x:t>Lower Coverplate</x:t>
+    <x:t>DHBW CAD-Data\BaseFrame\STL-Step-Dateien</x:t>
   </x:si>
   <x:si>
     <x:t>JointType: Fixed,  (XYZ) [0.00, 0.00, -30.00][mm], (RPY) [0.00, 0.00, 0.00][grad], (BOX) [L:300, W:140, H:2]</x:t>
@@ -455,6 +485,9 @@
   </x:si>
   <x:si>
     <x:t>Column19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Column20</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -514,13 +547,31 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
   </x:cellStyles>
+  <x:dxfs count="2">
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor auto="1"/>
+          <x:bgColor rgb="FFADD8E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor auto="1"/>
+          <x:bgColor rgb="FFF5F5DC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RobotPartList" displayName="RobotPartList" ref="A5:S87" totalsRowShown="0">
-  <x:autoFilter ref="A5:S87"/>
-  <x:tableColumns count="19">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RobotPartList" displayName="RobotPartList" ref="A5:V104" totalsRowShown="0">
+  <x:autoFilter ref="A5:V104"/>
+  <x:tableColumns count="22">
     <x:tableColumn id="1" name="LEVEL"/>
     <x:tableColumn id="2" name="Name"/>
     <x:tableColumn id="3" name="Type"/>
@@ -540,6 +591,9 @@
     <x:tableColumn id="17" name="Geometrie"/>
     <x:tableColumn id="18" name="Technology"/>
     <x:tableColumn id="19" name="Column19"/>
+    <x:tableColumn id="20" name="Column20"/>
+    <x:tableColumn id="21" name="ComponentType"/>
+    <x:tableColumn id="22" name="Template"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -833,8 +887,32 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W86"/>
+  <x:dimension ref="A1:W103"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.853482" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.567768" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42.996339" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12.567768" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="41.996339" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32.139196" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.567768" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15.710625" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="21.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="32.567768" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="21.424911" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="20.282054" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="11.567768" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="30.139196" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="92.567768" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="13.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="20" width="12.282054" style="0" customWidth="1"/>
+    <x:col min="21" max="21" width="18.282054" style="0" customWidth="1"/>
+    <x:col min="22" max="22" width="11.567768" style="0" customWidth="1"/>
+    <x:col min="23" max="23" width="19.567768" style="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="5" spans="1:23">
       <x:c r="A5" s="0" t="s">
@@ -892,7 +970,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="S5" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="T5" s="0" t="s">
+        <x:v>157</x:v>
       </x:c>
       <x:c r="U5" s="0" t="s">
         <x:v>18</x:v>
@@ -926,7 +1007,7 @@
     </x:row>
     <x:row r="7" spans="1:23">
       <x:c r="A7" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>26</x:v>
@@ -938,42 +1019,72 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G7" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="Q7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="U7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W7" s="0" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="W7" s="0" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:23">
       <x:c r="A8" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="G8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P8" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q8" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="U8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W8" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:23">
@@ -981,40 +1092,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G9" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="Q9" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P9" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="Q9" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="U9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:23">
@@ -1022,95 +1136,119 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="Q10" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P10" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="Q10" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="U10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:23">
       <x:c r="A11" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P11" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q11" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W11" s="0" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="W11" s="0" t="s">
-        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:23">
       <x:c r="A12" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>26</x:v>
+      <x:c r="P12" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W12" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:23">
@@ -1118,37 +1256,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G13" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="Q13" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U13" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W13" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:23">
@@ -1156,7 +1300,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>61</x:v>
@@ -1164,29 +1308,35 @@
       <x:c r="D14" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P14" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="Q14" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="U14" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:23">
@@ -1194,37 +1344,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G15" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P15" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Q15" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="U15" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W15" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:23">
@@ -1232,37 +1388,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G16" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P16" s="0" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G16" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I16" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P16" s="0" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="Q16" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="U16" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W16" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:23">
@@ -1270,7 +1432,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>74</x:v>
@@ -1278,122 +1440,170 @@
       <x:c r="D17" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
+        <x:v>77</x:v>
       </x:c>
       <x:c r="P17" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="Q17" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="U17" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:23">
       <x:c r="A18" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P18" s="0" t="s">
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q18" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="U18" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W18" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:23">
       <x:c r="A19" s="0">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L19" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="P19" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="Q19" s="0" t="s">
+        <x:v>88</x:v>
       </x:c>
       <x:c r="U19" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W19" s="0" t="s">
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:23">
       <x:c r="A20" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G20" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L20" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="M20" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="P20" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="Q20" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I20" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P20" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="Q20" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="U20" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W20" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:23">
@@ -1401,133 +1611,172 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L21" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q21" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="U21" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W21" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:23">
       <x:c r="A22" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L22" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
       <x:c r="P22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q22" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="U22" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W22" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:23">
       <x:c r="A23" s="0">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L23" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="M23" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="P23" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="Q23" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="U23" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W23" s="0" t="s">
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:23">
       <x:c r="A24" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P24" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L24" s="0" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="Q24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="U24" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W24" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:23">
@@ -1535,37 +1784,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L25" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P25" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q25" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I25" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P25" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="Q25" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="U25" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W25" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:23">
@@ -1573,37 +1828,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L26" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P26" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="Q26" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I26" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P26" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="Q26" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="U26" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W26" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:23">
@@ -1611,127 +1872,163 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L27" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P27" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="Q27" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I27" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P27" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="Q27" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="U27" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W27" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:23">
       <x:c r="A28" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P28" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L28" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q28" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U28" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W28" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:23">
       <x:c r="A29" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L29" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P29" s="0" t="s">
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q29" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U29" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W29" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:23">
       <x:c r="A30" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L30" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P30" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="Q30" s="0" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U30" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W30" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:23">
@@ -1739,40 +2036,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L31" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P31" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="Q31" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="U31" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W31" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:23">
@@ -1780,40 +2080,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L32" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P32" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Q32" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="U32" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W32" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:23">
@@ -1821,54 +2124,87 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L33" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P33" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Q33" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="U33" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W33" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:23">
       <x:c r="A34" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L34" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="P34" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="Q34" s="0" t="s">
+        <x:v>76</x:v>
       </x:c>
       <x:c r="U34" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W34" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:23">
@@ -1876,113 +2212,134 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L35" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P35" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q35" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="U35" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W35" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:23">
       <x:c r="A36" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L36" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
       <x:c r="P36" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q36" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="U36" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W36" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:23">
       <x:c r="A37" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L37" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="M37" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="P37" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="Q37" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I37" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P37" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="Q37" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="U37" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W37" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:23">
@@ -1990,107 +2347,134 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L38" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P38" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q38" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="U38" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W38" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:23">
       <x:c r="A39" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G39" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L39" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
       <x:c r="P39" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q39" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="U39" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W39" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:23">
       <x:c r="A40" s="0">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L40" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="M40" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="P40" s="0" t="s">
+        <x:v>95</x:v>
       </x:c>
       <x:c r="Q40" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="U40" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W40" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:23">
@@ -2098,19 +2482,37 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L41" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="Q41" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="U41" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W41" s="0" t="s">
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:23">
@@ -2118,40 +2520,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C42" s="0" t="s">
+      <x:c r="D42" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D42" s="0" t="s">
+      <x:c r="E42" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L42" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P42" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q42" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I42" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P42" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="Q42" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="U42" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W42" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:23">
@@ -2159,40 +2564,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C43" s="0" t="s">
+      <x:c r="E43" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D43" s="0" t="s">
+      <x:c r="F43" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G43" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L43" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P43" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G43" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H43" s="0" t="s">
+      <x:c r="Q43" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I43" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P43" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="Q43" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="U43" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W43" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:23">
@@ -2200,34 +2608,37 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G44" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L44" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P44" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G44" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H44" s="0" t="s">
+      <x:c r="Q44" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I44" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P44" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="Q44" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="U44" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W44" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:23">
@@ -2235,19 +2646,37 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C45" s="0" t="s">
+      <x:c r="F45" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G45" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L45" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="Q45" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="U45" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W45" s="0" t="s">
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:23">
@@ -2263,17 +2692,23 @@
       <x:c r="D46" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I46" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L46" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P46" s="0" t="s">
         <x:v>59</x:v>
@@ -2282,10 +2717,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="U46" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W46" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:23">
@@ -2301,17 +2736,23 @@
       <x:c r="D47" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I47" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L47" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P47" s="0" t="s">
         <x:v>64</x:v>
@@ -2320,10 +2761,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="U47" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W47" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:23">
@@ -2337,31 +2778,37 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G48" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I48" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L48" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P48" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="Q48" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="F48" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G48" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H48" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I48" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P48" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="Q48" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="U48" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W48" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:23">
@@ -2369,37 +2816,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G49" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I49" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L49" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P49" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="Q49" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F49" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G49" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H49" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I49" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P49" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="Q49" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="U49" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W49" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:23">
@@ -2407,124 +2860,175 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H50" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I50" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L50" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P50" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Q50" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="U50" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W50" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:23">
       <x:c r="A51" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I51" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L51" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="P51" s="0" t="s">
+        <x:v>78</x:v>
       </x:c>
       <x:c r="Q51" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="U51" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:23">
       <x:c r="A52" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G52" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H52" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I52" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L52" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P52" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="Q52" s="0" t="s">
+        <x:v>83</x:v>
       </x:c>
       <x:c r="U52" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W52" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:23">
       <x:c r="A53" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H53" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I53" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L53" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="P53" s="0" t="s">
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q53" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="U53" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W53" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:23">
@@ -2532,19 +3036,46 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G54" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I54" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L54" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
+      <x:c r="M54" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="P54" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="Q54" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="U54" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W54" s="0" t="s">
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:23">
@@ -2552,34 +3083,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G55" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H55" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D55" s="0" t="s">
+      <x:c r="I55" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L55" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P55" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="Q55" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="F55" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G55" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H55" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I55" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="Q55" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="U55" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W55" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:23">
@@ -2587,74 +3127,128 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E56" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G56" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H56" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I56" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L56" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="P56" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="Q56" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D56" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F56" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="U56" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W56" s="0" t="s">
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:23">
       <x:c r="A57" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D57" s="0" t="s">
-        <x:v>103</x:v>
+      <x:c r="E57" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H57" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I57" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L57" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="M57" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="P57" s="0" t="s">
+        <x:v>95</x:v>
       </x:c>
       <x:c r="Q57" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="U57" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W57" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:23">
       <x:c r="A58" s="0">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G58" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H58" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I58" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L58" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F58" s="0" t="s">
-        <x:v>102</x:v>
+      <x:c r="Q58" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="U58" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W58" s="0" t="s">
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:23">
@@ -2662,54 +3256,87 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H59" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I59" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L59" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P59" s="0" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="Q59" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="U59" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W59" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:23">
       <x:c r="A60" s="0">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G60" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H60" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I60" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L60" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F60" s="0" t="s">
-        <x:v>105</x:v>
+      <x:c r="P60" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="Q60" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="U60" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W60" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:23">
@@ -2717,133 +3344,163 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D61" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E61" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H61" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I61" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L61" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P61" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="Q61" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I61" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P61" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="Q61" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="U61" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W61" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:23">
       <x:c r="A62" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="E62" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H62" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I62" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P62" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L62" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q62" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U62" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W62" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:23">
       <x:c r="A63" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H63" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I63" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L63" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P63" s="0" t="s">
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q63" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U63" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W63" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:23">
       <x:c r="A64" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G64" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H64" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I64" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L64" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P64" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="Q64" s="0" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U64" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W64" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:23">
@@ -2851,34 +3508,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E65" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H65" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I65" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L65" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P65" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="Q65" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="U65" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W65" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:23">
@@ -2886,34 +3552,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H66" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I66" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L66" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P66" s="0" t="s">
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Q66" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="U66" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W66" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:23">
@@ -2921,34 +3596,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E67" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H67" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I67" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L67" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P67" s="0" t="s">
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Q67" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="U67" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W67" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:23">
@@ -2956,34 +3640,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E68" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H68" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I68" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L68" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="P68" s="0" t="s">
+        <x:v>78</x:v>
       </x:c>
       <x:c r="Q68" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="U68" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W68" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:23">
@@ -2991,168 +3684,222 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H69" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I69" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L69" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P69" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q69" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="U69" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W69" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:23">
       <x:c r="A70" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H70" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I70" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L70" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
       <x:c r="P70" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q70" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="U70" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W70" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:23">
       <x:c r="A71" s="0">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E71" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H71" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I71" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L71" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="M71" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="P71" s="0" t="s">
+        <x:v>95</x:v>
       </x:c>
       <x:c r="Q71" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="U71" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W71" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:23">
       <x:c r="A72" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E72" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G72" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H72" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="I72" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L72" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P72" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="Q72" s="0" t="s">
+        <x:v>99</x:v>
       </x:c>
       <x:c r="U72" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W72" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:23">
       <x:c r="A73" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E73" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H73" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I73" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L73" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="P73" s="0" t="s">
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q73" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="U73" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W73" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:23">
@@ -3160,54 +3907,84 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E74" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F74" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G74" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H74" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I74" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L74" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="M74" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="P74" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="Q74" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="U74" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W74" s="0" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="C74" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D74" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F74" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="U74" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:23">
       <x:c r="A75" s="0">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H75" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I75" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L75" s="0" t="s">
+        <x:v>111</x:v>
       </x:c>
       <x:c r="Q75" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="U75" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W75" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:23">
@@ -3215,360 +3992,1191 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G76" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H76" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I76" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L76" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="Q76" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="U76" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W76" s="0" t="s">
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:23">
       <x:c r="A77" s="0">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="E77" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H77" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I77" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L77" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P77" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="Q77" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I77" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P77" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="Q77" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="U77" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W77" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:23">
       <x:c r="A78" s="0">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E78" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F78" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="F78" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
       <x:c r="G78" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H78" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I78" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L78" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="P78" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="Q78" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="U78" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W78" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:23">
       <x:c r="A79" s="0">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H79" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I79" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L79" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P79" s="0" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="Q79" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="U79" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W79" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:23">
       <x:c r="A80" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F80" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G80" s="0">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="F80" s="0" t="s">
-        <x:v>129</x:v>
+      <x:c r="H80" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I80" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L80" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="Q80" s="0" t="s">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="U80" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W80" s="0" t="s">
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:23">
       <x:c r="A81" s="0">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H81" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I81" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L81" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="P81" s="0" t="s">
+        <x:v>117</x:v>
       </x:c>
       <x:c r="Q81" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="U81" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W81" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:23">
       <x:c r="A82" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G82" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H82" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I82" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L82" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="P82" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="Q82" s="0" t="s">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="U82" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W82" s="0" t="s">
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:23">
       <x:c r="A83" s="0">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G83" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H83" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I83" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L83" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="P83" s="0" t="s">
+        <x:v>125</x:v>
       </x:c>
       <x:c r="Q83" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="U83" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W83" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:23">
       <x:c r="A84" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G84" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H84" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I84" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L84" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="Q84" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I84" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P84" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="Q84" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="U84" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W84" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:23">
       <x:c r="A85" s="0">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G85" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H85" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I85" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L85" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="P85" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="Q85" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I85" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P85" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="Q85" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
       <x:c r="U85" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W85" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:23">
       <x:c r="A86" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F86" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G86" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H86" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I86" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L86" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="P86" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="Q86" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="U86" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W86" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:23">
+      <x:c r="A87" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E87" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F87" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G87" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H87" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I87" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L87" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="P87" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="Q87" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="U87" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W87" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:23">
+      <x:c r="A88" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F88" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G88" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H88" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I88" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L88" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="Q88" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="U88" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W88" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:23">
+      <x:c r="A89" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F89" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G89" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H89" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I89" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L89" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P89" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="Q89" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="U89" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W89" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:23">
+      <x:c r="A90" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F90" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G90" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H90" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I90" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L90" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P90" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="Q90" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="U90" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W90" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:23">
+      <x:c r="A91" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E91" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F91" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G91" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H91" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I91" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L91" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P91" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="Q91" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="U91" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W91" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:23">
+      <x:c r="A92" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E92" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F92" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G92" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H92" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I92" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L92" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="P92" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="Q92" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="U92" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W92" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:23">
+      <x:c r="A93" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="E93" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F93" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G93" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H93" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I93" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L93" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="P93" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="Q93" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="U93" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W93" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:23">
+      <x:c r="A94" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F94" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G94" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H94" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I94" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L94" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="Q94" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="U94" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W94" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:23">
+      <x:c r="A95" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E95" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F95" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G95" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H95" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I95" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L95" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="P95" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="Q95" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="U95" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W95" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:23">
+      <x:c r="A96" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="E96" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F96" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G96" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H96" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I96" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L96" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="P96" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="Q96" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="U96" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W96" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:23">
+      <x:c r="A97" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G97" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H97" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I97" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L97" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="Q97" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="U97" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W97" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:23">
+      <x:c r="A98" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F98" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G98" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H98" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I98" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L98" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="P98" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="Q98" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="U98" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W98" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:23">
+      <x:c r="A99" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F99" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G99" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H99" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I99" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L99" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="P99" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="Q99" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="U99" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W99" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:23">
+      <x:c r="A100" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F100" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G100" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H100" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I100" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L100" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="Q100" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="U100" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W100" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:23">
+      <x:c r="A101" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F101" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G101" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H101" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I101" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L101" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="P101" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="Q101" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="U101" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W101" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:23">
+      <x:c r="A102" s="0">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C86" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D86" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="E86" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F86" s="0" t="s">
+      <x:c r="B102" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E102" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F102" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G86" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H86" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I86" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="P86" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="Q86" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="U86" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="W86" s="0" t="s">
+      <x:c r="G102" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H102" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I102" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L102" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P102" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="Q102" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="U102" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W102" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
+    <x:row r="103" spans="1:23">
+      <x:c r="A103" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="E103" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F103" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G103" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H103" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I103" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L103" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="P103" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="Q103" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="U103" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W103" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="A6:V104">
+    <x:cfRule type="expression" dxfId="0" priority="1" operator="equal">
+      <x:formula>$A6=1</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="1" priority="2" operator="equal">
+      <x:formula>$A6=2</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
